--- a/debug/judgements_intro/excel_overviews/gpt-4.1_vs_Llama-2-7b-chat-hf/phi-4/metrics_default_vs_aae.xlsx
+++ b/debug/judgements_intro/excel_overviews/gpt-4.1_vs_Llama-2-7b-chat-hf/phi-4/metrics_default_vs_aae.xlsx
@@ -420,25 +420,25 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>0.8345864661654135</v>
+        <v>0.8382352941176471</v>
       </c>
       <c r="B2">
         <v>0</v>
       </c>
       <c r="C2">
-        <v>0.8098591549295775</v>
+        <v>0.8028169014084507</v>
       </c>
       <c r="D2">
-        <v>0.1956521739130435</v>
+        <v>0.1971830985915493</v>
       </c>
       <c r="E2">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="F2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G2">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
